--- a/AV-1/curadoria_final_Victor_G4.xlsx
+++ b/AV-1/curadoria_final_Victor_G4.xlsx
@@ -425,127 +425,107 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>question_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>question_number</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>exam_id</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>turns</t>
+          <t>exam_year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>values</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>nullified</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Disciplina</t>
+          <t>question</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>choices</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">answerKey		</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Lei</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>URN</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42_direito_penal_questao_1</t>
+          <t>Em relação às obrigações assumidas por Olímpio Noronha, assinale a alternativa correta.","{'text': [São válidas tanto as obrigações assumidas no exercício da empresa quanto estranhas a essa atividade e por elas Olímpio Noronha responderá ilimitadamente., 'São nulas todas as obrigações assumidas, porque Olímpio Noronha não pode ser empresário concomitantemente com o serviço público militar.', 'São válidas apenas as obrigações estranhas ao exercício da empresa, pelas quais Olímpio Noronha responderá ilimitadamente	 as demais são nulas.'</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42_direito_penal</t>
+          <t xml:space="preserve"> São válidas apenas as obrigações relacionadas ao exercício da empresa e por elas Olímpio Noronha responderá limitadamente	" as demais são anuláveis.]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QUESTÃO 1
-Frederico, policial, caminha à paisana quando vê um cachorro feroz avançar na direção de crianças que brincavam na rua. Frederico, imediatamente, sacou sua arma e a apontou na direção do cachorro, com o intuito de impedir o ataque.
-Jonas, que estava na janela de sua residência, mantém sob sua guarda arma de fogo legalmente registrada, ante sua autorização de posse, e tem visão parcial da situação. Ele vê apenas um homem (Frederico) apontando uma arma na direção das crianças que brincavam na rua, sem perceber a aproximação do cachorro raivoso. Assim, Jonas, acreditando que Frederico representava uma ameaça à integridade física das crianças, violando o dever de diligência e cuidado que deveria adotar em situações como a apresentada, imediatamente efetua disparo de arma de fogo contra Frederico, que cai, sem vida, após ser atingido pelo projétil da arma de fogo de Jonas. Com isso, o cachorro prosseguiu o ataque às crianças, fato que, isoladamente, levou uma delas a óbito.
-Comprovados os fatos tais como aqui relatados, Jonas é denunciado por duplo homicídio doloso, sendo-lhe imputadas as mortes de Frederico e da criança. Como advogado(a) de Jonas, responda às questões a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['A) Qual a tese de Direito Penal a ser sustentada em relação à imputação de homicídio contra Frederico? Fundamente. (Valor: 0,65)', 'B) Qual a tese de Direito Penal a ser sustentada em relação à imputação de homicídio contra a criança? Fundamente. (Valor: 0,60)']</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[0.65, 0.6000000000000001]</t>
+          <t xml:space="preserve"> C</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> D]}""</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Direito Penal</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+          <t>A"</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,64 +537,48 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42_direito_penal_questao_2</t>
+          <t>Considerando o caso narrado e as regras sobre Audiência de Instrução e Julgamento previstas no Código de Processo Civil, assinale a afirmativa correta.","{'text': ['A audiência designada para o dia 24.01.2014 é una e contínua, todavia, não sendo possível concluir, num só dia, a instrução, o debate e o julgamento, o juiz marcará o seu prosseguimento para dia próximo.', 'Mateus e Tiago poderão, por comum acordo, quantas vezes entenderem oportuno e conveniente, requerer o adiamento da audiência designada, desde que seja protocolado o pedido com antecedência mínima de 45 dias da data marcada.', 'Concluída a instrução, o magistrado dará a palavra ao advogado de Tiago (réu) e ao de Mateus (autor), sucessivamente, pelo prazo de 40 minutos para cada um, admitindo expressamente o Código de Processo Civil a substituição do debate oral por memoriais, a serem apresentados no prazo máximo de 10 dias.', 'Na audiência de instrução designada para o dia 24.01.2014, as provas a serem produzidas obedecerão à seguinte ordem: oitiva de testemunhas arrolados pelo autor e pelo réu	 depoimento pessoal do autor e do réu	" e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>42_direito_penal</t>
+          <t xml:space="preserve"> por fim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QUESTÃO 2
-Rui, 20 anos, inconformado com o término do relacionamento com Vânia, também com 20 anos, divulgou fotos da ex-companheira nua. Em razão disso, foi denunciado e, depois do regular processamento da ação penal, foi condenado, nos termos do Art. 218-C, § 1º, do CP, à pena de um ano e quatro meses de reclusão, substituída por duas restritivas de direitos, consistentes em prestação pecuniária e multa.
-O Ministério Público foi intimado da condenação, não tendo apresentado o recurso cabível no prazo legal. Vânia e seu(ua) advogado(a) foram intimados da sentença, porém, até o momento, Vânia não havia se habilitado como assistente de acusação, ainda que não concorde com as penas substitutivas aplicadas.
-Como advogado(a) de Vânia, responda às questões a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> prestação de esclarecimentos do perito e dos assistentes técnicos aos quesitos formulados pelas partes.']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['A) Qual a tese de Direito Penal a ser sustentada para a reforma da sentença condenatória? Justifique. (Valor: 0,60)', 'B) Qual o recurso a ser interposto pela vítima e qual o prazo de interposição? Justifique, identificando o início da contagem do prazo. (Valor: 0,65)']</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[0.6000000000000001, 0.65]</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Direito Penal</t>
+          <t xml:space="preserve"> D]}""</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>A"</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -626,64 +590,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42_direito_penal_questao_3</t>
+          <t>II. Joaquim constrange Benedita</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>42_direito_penal</t>
+          <t xml:space="preserve"> por meio de grave ameaça</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>QUESTÃO 3
-Douglas foi denunciado pela prática do delito de trânsito de participação em corrida do tipo "racha" (Art. 308 da Lei nº 9.503/1997 - CTB) e por falsa identidade (Art. 307 do CP). A denúncia foi recebida no dia 10/02/2020. Em razão da pandemia do Coronavírus-19, os autos ficaram paralisados aguardando a retomada da pauta de audiências presenciais do Juízo, o que somente aconteceu em 2022. Assim, em 10/10/2023, Douglas foi condenado como incurso nas penas do Art. 308 do CTB e absolvido em relação ao delito do Art. 307 do Código Penal, por falta de provas.
-Apenas o Ministério Público interpôs tempestiva apelação, postulando a condenação de Douglas pelo delito de falsa identidade. Por maioria, o Tribunal de Justiça denegou o recurso de apelação, mantendo na íntegra a sentença recorrida, o que motivou a oposição de embargos infringentes por parte do Ministério Público.
-Como advogado(a) de Douglas, você foi intimado, no dia 10/09/2024, para apresentar suas contrarrazões. Assim, com base nos dados do enunciado, responda às questões a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> a ter com ele relação sexual. Após o coito Benedita falece em decorrência de ataque cardíaco</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['A) Qual a tese de extinção da punibilidade que, neste momento, pode ser deduzida por Douglas? Fundamente, identificando sobre qual fato recai. (Valor: 0,60)', 'B) Indique a tese processual que deve ser arguida em face do recurso oposto pelo MP. Justifique. (Valor: 0,65)']</t>
+          <t xml:space="preserve"> pois padecia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0.6000000000000001, 0.65]</t>
+          <t xml:space="preserve"> desde criança</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> de cardiopatia grave</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Direito Penal</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+          <t xml:space="preserve"> condição desconhecida por Joaquim.		</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -695,65 +639,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>42_direito_penal_questao_4</t>
+          <t>Diante da hipótese apresentada, assinale a afirmativa correta.","{'text': ['As gorjetas integram a remuneração, mas não servem de base de cálculo para o pagamento do aviso prévio, adicional noturno, horas-extras e repouso semanal remunerado.', 'As gorjetas não integram a remuneração, uma vez que são espontâneas, pois não há o controle das quantias concedidas.', 'As gorjetas são integradas, para todos os efeitos, na remuneração do empregado, repercutindo, assim, no pagamento de todos os direitos trabalhistas.', 'As gorjetas integram a remuneração apenas para efeitos de aviso prévio trabalhado, adicional noturno, horas-extras e repouso semanal remunerado, pois as demais parcelas não estão relacionadas com o dia a dia de trabalho efetivo	" não havendo trabalho</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42_direito_penal</t>
+          <t xml:space="preserve"> não há gorjeta.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QUESTÃO 4
-Thiago cumpria pena em regime semiaberto quando preencheu os requisitos objetivos para progredir ao regime aberto, tendo formulado o requerimento respectivo.
-O Juiz, ao apreciar o pedido, condicionou a efetiva progressão à existência de vaga em casa de albergado, que, no momento, encontrava-se lotada, devendo o condenado aguardar na unidade de semiaberto.
-Thiago interpôs agravo em execução, de forma que o Juiz reconsiderou a decisão anterior e permitiu que Thiago cumprisse o restante da pena em albergue domiciliar, desde que se comprometesse à prestação de serviços à comunidade como condição especial do regime aberto, na forma do Art. 113 da LEP.
-Como advogado(a) de Thiago, responda às questões a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['A) A inexistência de vaga no regime mais brando pode impedir a progressão de regime? Justifique. (Valor: 0,65)', 'B) É cabível a imposição de prestação de serviços à comunidade como condição especial do regime aberto? Justifique. (Valor: 0,60)']</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0.65, 0.6000000000000001]</t>
+          <t xml:space="preserve"> C</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> D]}""</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Direito Penal</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t xml:space="preserve">A"	</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -765,65 +688,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42_direito_tributario_peca_profissional</t>
+          <t>De acordo com a fórmula de Radbruch,","{'text': ['embora as leis injustas sejam válidas e devam ser obedecidas, as leis extremamente injustas perderão a validade e o próprio caráter de jurídicas, sendo, portanto, dispensada sua obediência.', 'apenas a lei justa pode ser considerada jurídica, pois a lei injusta não será direito.', 'o direito é o mínimo ético de uma sociedade, de forma que qualquer lei injusta não será direito.', 'o direito natural é uma concepção superior ao positivismo jurídico	" por isso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>42_direito_tributario</t>
+          <t xml:space="preserve"> a justiça deve sempre prevalecer sobre a segurança.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PEÇA PRÁTICO-PROFISSIONAL
-A sociedade empresária ABC Ltda., com estabelecimento no Município X (sede de comarca de Vara Única), especializada em reciclagem de lixo, foi contratada para prestar serviços de remoção, tratamento e reciclagem de lixo no Município Y, local onde recolheu o Imposto sobre Serviços (ISS) devido naquela operação.
-Meses após, recebeu uma notificação de débito da Secretaria de Fazenda do Município X cobrando o ISS daquele serviço prestado no Município Y, sob a alegação de possuir estabelecimento fixo em seu território. Na notificação, foi aplicada uma multa de 150% do valor do imposto cobrado e a sociedade empresária foi advertida de que, caso não pagasse a dívida no prazo de 30 (trinta) dias, teria o seu estabelecimento interditado.
-A sociedade empresária o(a) contratou, como advogado(a), para defender seus interesses e promover a medida judicial cabível, tendo urgência sobretudo em razão da ameaça de interdição do estabelecimento. Por se tratar de serviço de reciclagem de lixo, a sociedade empresária precisará comprovar o exato local em que o realizou, devendo juntar fotos e requerer prova pericial.
-Diante dos fatos expostos, redija a medida judicial cabível para que seu cliente não tenha que pagar tal tributo e respectiva multa, nem tenha seu estabelecimento interditado, ciente de que será necessária dilação probatória. (Valor: 5,00)
-Obs .: a peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[5.0]</t>
+          <t xml:space="preserve"> C</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> D]}""</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Direito Tributario</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+          <t xml:space="preserve">A"	</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -835,63 +737,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42_direito_tributario_questao_1</t>
+          <t>Sobre a situação hipotética descrita acima, assinale a opção correta.","{'text': ['O ato de improbidade pode estar configurado com a mera comunicação, antes da divulgação oficial, da medida a ser adotada pela prefeitura, que valorizará determinados imóveis, ainda que não tenha havido qualquer vantagem para Caio.', 'A configuração da improbidade administrativa depende, sempre, da existência de enriquecimento ilícito por parte de Caio ou de lesão ao erário, requisitos ausentes no caso concreto.', 'Caio, caso venha a ser condenado criminalmente pela prática das condutas acima descritas, não poderá responder por improbidade administrativa, sob pena de haver bis in idem.', 'Caio não responde por ato de improbidade, por não ser servidor de carreira	" responde</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42_direito_tributario</t>
+          <t xml:space="preserve"> todavia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QUESTÃO 1
-José Silva, inconformado com o fato de ter pago, nos últimos dois anos, taxa municipal de combate a incêndios que reputa indevida, protocoliza pedido administrativo de restituição do indébito tributário junto ao Fisco municipal. Contudo, a decisão final na esfera administrativo-tributária lhe é desfavorável, de modo que José decide contratar você, como advogado(a), requerendo que entre com ação anulatória da decisão administrativa que denegou a restituição.
-Diante desse cenário, responda aos itens a seguir.
-Obs .: o(a) examinando(a) deve fundamentar sua resposta. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> por crime de responsabilidade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['A) Qual o prazo prescricional para propositura dessa ação anulatória da decisão administrativa que denegou a restituição? Fundamente. (Valor: 0,60)', 'B) Tem razão Jose em sua insurgencia contra o pagamento dessa taxa municipal de combate de incêndios? Justifique, indicando o fundamento legal. (Valor: 0,65)']</t>
+          <t xml:space="preserve"> na qualidade de agente político</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[0.6000000000000001, 0.65]</t>
+          <t xml:space="preserve"> ocupante de cargo em comissão.']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Direito Tributario</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t xml:space="preserve"> C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> D]}""</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -903,64 +794,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42_direito_tributario_questao_2</t>
+          <t>A partir da hipótese apresentada, assinale a opção correta.","{'text': ['Marina marca uma reunião entre o vendedor e Mônica, mas o negócio não se realiza por arrependimento das partes. Sem pagar a comissão, Mônica dispensa Marina, que reclama seu pagamento, explicando que conseguiu o negócio e que não importa se não ocorreu a compra da sala.', 'Passado o prazo contratual para a obtenção do negócio, o próprio vendedor entra em contato com Mônica para celebrar o negócio, liberando-a, portanto, de pagar a comissão de Marina.', 'Como a obrigação de Marina é apenas de obtenção do negócio, a responsabilidade pela segurança e pelo risco é apenas do vendedor, sendo desnecessário que Marina se procupe com esses detalhes.', 'A remuneração de Marina deve ser previamente ajustada entre as partes	" caso contrário</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>42_direito_tributario</t>
+          <t xml:space="preserve"> Mônica pagará o valor que achar suficiente.']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>QUESTÃO 2
-Lei Ordinária Municipal nº XXX, de 1º de outubro de 2022, alterou todas as alíquotas do Imposto sobre Serviços (ISS) previstas na Lei Complementar Municipal nº YYY/2015, majorando-as de 2% para 5%.
-A Barbearia Júpiter Ltda. foi autuada em janeiro de 2023, por diferenças nos valores recolhidos de Imposto sobre Serviços (ISS) dos anos de 2019 a 2021, pela aplicação da nova alíquota de 5%, tendo o auditor fiscal consignado expressamente que teria adotado as alíquotas da nova lei, uma vez que seria a norma vigente no momento da lavratura do auto de infração, inclusive citando o brocardo latino "tempus regit actum".
-Inconformada com essa cobrança, a barbearia contrata você, como advogado(a), para defender seus interesses. Diante desse cenário, responda aos itens a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['A) O auditor fiscal agiu corretamente ao aplicar a alíquota majorada, prevista na nova lei, na lavratura do auto de infração, cobrando a diferença do Imposto sobre Serviços (ISS)? Justifique. (Valor: 0,65)', 'B) A nova lei ordinária municipal poderia alterar tal alíquota de ISS para 5%? Justifique. (Valor: 0,60)']</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[0.65, 0.6000000000000001]</t>
+          <t xml:space="preserve"> C</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> D]}""</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Direito Tributario</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+          <t xml:space="preserve">A"	</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -972,63 +843,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42_direito_tributario_questao_3</t>
+          <t>Sobre a situação apresentada no enunciado, assinale a opção correta.","{'text': ['Maria Clara sofreu coação para fechar o negócio, diante da insistência do antigo proprietário e, por isso, pode ser proposta a anulação do negócio jurídico no prazo máximo de três anos.', 'O negócio efetuado por Maria Clara não poderá ser anulado porque decorreu de manifestação de vontade por parte da adquirente. Dessa forma, como não se trata de relação de consumo, Maria Clara não possui essa garantia.', 'O pai de Maria Clara, inconformado com a situação, pretende anular o negócio efetuado pela filha, porém, como já se passaram três anos, isso não será mais possível, pois já decaiu seu direito.', 'O negócio jurídico efetuado por Maria Clara pode ser anulado	" porém</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>42_direito_tributario</t>
+          <t xml:space="preserve"> se o antigo proprietário concordar com a diminuição no preço</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>QUESTÃO 3
-O Estado Alfa editou uma nova lei sobre IPVA, alterando as alíquotas originalmente estabelecidas desse tributo, de maneira a fixar duas alíquotas diferenciadas (4% e 2%) em razão do uso do automóvel como carro de passeio e como táxi, respectivamente. A mesma lei estabeleceu também uma alíquota majorada de 10% em relação àquela incidente sobre os automóveis nacionais, caso o automóvel seja importado.
-Diante desse cenário, responda aos itens a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> o vício no contrato estará sanado.']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['A) É válida a adoção de alíquotas diferenciadas de IPVA em razão do uso do automóvel como carro de passeio e como táxi? Justifique. (Valor: 0,60)', 'B) É válida a alíquota diferenciada para automóveis importados? Justifique. (Valor: 0,65)']</t>
+          <t xml:space="preserve"> 'label': [A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[0.6000000000000001, 0.65]</t>
+          <t xml:space="preserve"> B</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> C</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Direito Tributario</t>
+          <t xml:space="preserve"> D]}""</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t xml:space="preserve">D"	</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Legislação Geral</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1040,281 +896,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>42_direito_tributario_questao_4</t>
+          <t>Sobre o caso apresentado, de acordo com as disposições do Código Civil, assinale a opção correta.","{'text': ['É vedada a participação de mais de um sócio ostensivo na sociedade em conta de participação	" logo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>42_direito_tributario</t>
+          <t xml:space="preserve"> as demais sócias não poderão ter a qualidade de sócio ostensivo.'</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>QUESTÃO 4
-Um projeto de lei estadual de iniciativa do Tribunal de Justiça do Estado Alfa pretende alterar a divisão das comarcas judiciais nesse ente federado. Além dessa alteração, em um de seus artigos, foi prevista a instituição de uma nova isenção da taxa judiciária. Foi apresentada a estimativa do impacto financeiro e orçamentário referente à concessão da nova isenção.
-No momento em que cabia ao Governador sancionar o projeto de lei, na parte referente à isenção, houve veto, sob dois argumentos: i) a lei isentiva tributária estava mesclada com tema de organização judiciária; ii) foi violada a reserva de iniciativa para leis em matéria tributária, que seria do Chefe do Executivo, por aplicação do princípio da simetria quanto ao Presidente da República, conforme o Art. 61, §1º, inciso II, alínea b, da CRFB/88.
-Diante desse cenário, responda aos itens a seguir.
-Obs .: o(a) examinando(a) deve fundamentar sua resposta. A mera citação do dispositivo legal não confere pontuação.</t>
+          <t xml:space="preserve"> As sócias participantes Januária e Cristina poderão fiscalizar a gestão dos negócios sociais pela sócia ostensiva Mariana.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>['A) Tem razão o Governador em seu argumento de que não poderia haver mescla de lei isentiva tributária com tema de organização judiciária? Justifique. (Valor: 0,60)', 'B) Tem razão o Governador em seu argumento de que foi violada a reserva de iniciativa em matéria tributária, que seria do Chefe do Executivo por aplicação do princípio da simetria quanto ao Presidente da República? Justifique (Valor: 0,65)']</t>
+          <t xml:space="preserve"> 'A sociedade em conta de participação deverá adotar como nome empresarial firma social</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[0.6000000000000001, 0.65]</t>
+          <t xml:space="preserve"> da qual deverá fazer parte a sócia ostensiva.'</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
+          <t xml:space="preserve"> 'A sociedade somente poderá existir se o contrato não estiver inscrito em qualquer registro</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Direito Tributario</t>
+          <t xml:space="preserve"> pois é uma sociedade não personificada.']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t xml:space="preserve"> 'label': [A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> B</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Legislação Geral</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>42_direito_empresarial_peca_profissional</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>42_direito_empresarial</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PEÇA PRÁTICO-PROFISSIONAL
-A companhia fechada Comercial e Exportadora Três Pontas S.A., cujo objeto é a exportação de café de alta qualidade, passa por grave crise financeira em razão da pandemia de 2020 e de 2021, além dos efeitos de forte geada na região sul de Minas Gerais, em 2022, que afetou as plantações de café, diminuindo sensivelmente a safra, sobretudo em cafés de alta qualidade. A sociedade foi regularmente constituída em 1970 e tem sua sede e seu único estabelecimento em Caxambu, MG.
-O balanço patrimonial do ano de 2020 já acusava um prejuízo líquido de R$ 2.000.000,00 (dois milhões de reais), que aumentou para R$ 6.000.000,00 (seis milhões de reais) e para R$ 14.000.000,00 (catorze milhões de reais). Atualmente, o valor total do passivo que precisa ser renegociado e novado é de R$ 17.000.000,00 (dezessete milhões de reais). Existem demandas trabalhistas provenientes de rescisões de contratos de trabalho que comprometem o fluxo de caixa, e a sociedade está há cinco meses sem Certidão Negativa de Débito (CND) por não ter condição de renová-la.
-As receitas da companhia vinham crescendo e seu fluxo de caixa era positivo até o primeiro semestre de 2020. A partir de então, o volume de receita com as exportações caiu mais de 80%, mas vinha se recuperando lentamente. Todavia, com a geada de 2022, voltou a cair. A receita atual é apenas de 45% do que era em 2019.
-Mesmo com cortes no número de empregados, redução salarial, férias coletivas e alienação de um imóvel para obter recursos para pagar credores, a situação está longe de se normalizar. O acionista controlador investiu R$ 2.000.000,00 (dois milhões de reais) no segundo semestre de 2022, mas esse valor é de longa recuperação, pois depende da atividade da sociedade. Contudo, existe perspectiva de melhora a médio prazo em razão da alta do preço da commodity no mercado internacional e da volta de alguns clientes internacionais da União Europeia.
-Você, como advogado(a), é procurado(a) pelo Diretor-Presidente e representante legal, Dr. Caldas Botelho, que lhe pede o ajuizamento de medida para superar a crise por que passa a devedora, permitindo seu saneamento e, sobretudo, afastar a possibilidade de decretação de falência.
-A sociedade já sofreu dois pedidos de falência, que puderam ser afastados com depósito elisivo, mas não se sabe até quando ela terá êxito em casos futuros.
-O Dr. Caldas Botelho informou também que a companhia já aprovou a medida em Assembleia Geral extraordinária, conforme documento que lhe entregou.
-Considerando que a Comarca de Caxambu, MG, é de vara única, elabore a peça processual adequada. (Valor: 5.00)
-Obs .: a peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[5.0]</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Direito Empresarial</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Código Civil</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Lei nº 10.406/2002</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>urn:lex:br:federal:lei:2002-01-10;10406</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>http://www.planalto.gov.br/ccivil_03/leis/2002/l10406compilada.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>42_direito_empresarial_questao_1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>42_direito_empresarial</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>QUESTÃO 1
-Os sócios da sociedade limitada Adelândia Bar e Restaurante Ltda. deliberaram por unanimidade a alienação do único estabelecimento, situado na cidade de Trindade, GO.
-Após a alienação, que foi feita sem qualquer notificação prévia aos credores ou sem qualquer pagamento a eles, não restaram no patrimônio da pessoa jurídica bens suficientes para solver o seu passivo.
-Diante da situação narrada, responda aos itens a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>['A) Qual medida prevista na legislação empresarial poderá ser tomada por qualquer dos credores da sociedade empresária diante da alienação do estabelecimento? Justifique. (Valor: 0,60)', 'B) Qual o efeito da deliberação dos sócios no tocante à aprovação da alienação do estabelecimento sobre a responsabilidade de cada um na sociedade? Justifique. (Valor: 0,65)']</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>[0.6000000000000001, 0.65]</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Direito Empresarial</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Código Civil</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Lei nº 10.406/2002</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>urn:lex:br:federal:lei:2002-01-10;10406</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>http://www.planalto.gov.br/ccivil_03/leis/2002/l10406compilada.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>42_direito_empresarial_questao_2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>42_direito_empresarial</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>QUESTÃO 2
-O empresário individual Ubiratã pretendia vender três carros executivos de sua frota e, para tanto, contratou dois corretores com o fito de mediar a venda, ambos sem cláusula de exclusividade.
-O primeiro corretor foi atuante na transmissão das propostas ao cliente e o segundo prestou todos os esclarecimentos acerca da segurança do negócio. Por questões pessoais, a venda mediada pelos corretores não se concretizou diante da desistência de Ubiratã na véspera do dia marcado para a assinatura do contrato.
-Com base nos fatos narrados e nas disposições sobre o contrato de corretagem, excluída a possibilidade de arrependimento do cliente, responda aos itens a seguir.
-Obs .: o(a) examinando(a) deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>['A) Ubiratã deve comissão aos dois corretores? Justifique. (Valor: 0,65)', 'B) Caso o negócio pretendido por Ubiratã e mediado pelos corretores se concluísse, qual seria a regra para o pagamento da comissão? Justifique. (Valor: 0,60)']</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[0.65, 0.6000000000000001]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é um bacharel em direito que está realizando a segunda fase da prova da Ordem dos Advogados do Brasil (OAB), organizada pela FGV. Sua tarefa é responder às questões discursivas e elaborar uma peça processual, demonstrando seu conhecimento jurídico, capacidade de raciocínio e habilidade de aplicar a legislação e jurisprudência pertinentes ao caso apresentado.
-# ATENÇÃO
-Na elaboração dos textos da peça prático-profissional e das respostas às questões discursivas, você deverá incluir todos os dados que se façam necessários, sem, contudo, produzir qualquer identificação ou informações além daquelas fornecidas e permitidas nos enunciados contidos no caderno de prova. A omissão de dados que forem legalmente exigidos ou necessários para a correta solução do problema proposto acarretará em descontos na pontuação atribuída a você nesta fase. Você deve estar atento para não gerar nenhum dado diferente que dê origem a uma marca identificadora.
-A detecção de qualquer marca identificadora no espaço destinado à transcrição dos textos definitivos acarretará a anulação da prova prático-profissional e a eliminação de você. Assim, por exemplo, no fechamento da peça, você deve optar por utilizar apenas “reticências” ou “XXX”, ou seja: data “...” ou Data “XXX”, local “...” ou Local “XXX”, Advogado “...” ou Advogado “XXX”, inscrição OAB “...” ou Inscrição OAB “XXX”, destacando-se que, no corpo das respostas, você não deverá criar nenhum dado gerador de marca de identificação.
-# OBSERVAÇÔES
-PEÇA PRÁTICO-PROFISSIONAL: A peça deve abranger todos os fundamentos de Direito que possam ser utilizados para dar respaldo à pretensão. A simples menção ou transcrição do dispositivo legal não confere pontuação.
-QUESTÃO: Você deve fundamentar suas respostas. A mera citação do dispositivo legal não confere pontuação.
-A partir de agora, todas as suas respostas comporão o texto definitivo (não o caderno de rascunhos).
-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Direito Empresarial</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Código Civil</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Lei nº 10.406/2002</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>urn:lex:br:federal:lei:2002-01-10;10406</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>http://www.planalto.gov.br/ccivil_03/leis/2002/l10406compilada.htm</t>
         </is>
       </c>
     </row>
